--- a/experiment/Omni+CNN_2CH_bestx4/Collect/Omni_Collect.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/Collect/Omni_Collect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gama\Desktop\New folder\Omni\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\Desktop\New folder\Omni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7378922-52FB-46B8-B015-F431DFE08AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F93C92-B76C-4A3F-B828-0B72E1243F1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSNR" sheetId="1" r:id="rId1"/>
@@ -33,16 +33,16 @@
     <t>DHTCUN</t>
   </si>
   <si>
-    <t>Omni + CNN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omni _2CH </t>
-  </si>
-  <si>
     <t>Omni</t>
   </si>
   <si>
-    <t>Omni+CNN _2CH</t>
+    <t>Omni+CNN_2CH</t>
+  </si>
+  <si>
+    <t>Omni+CNN</t>
+  </si>
+  <si>
+    <t>Omni_2CH</t>
   </si>
 </sst>
 </file>
@@ -53,14 +53,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -112,14 +112,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -397,135 +397,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F407"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F411"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>28.780999999999999</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>28.946000000000002</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>28.164000000000001</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>29.02</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>27.387</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>29.039000000000001</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>29.716000000000001</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>29.672999999999998</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>29.373000000000001</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>29.713999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>29.233000000000001</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>30.437000000000001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>30.600999999999999</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>30.356999999999999</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>30.036000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>28.885000000000002</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>30.481000000000002</v>
       </c>
       <c r="D5">
         <v>30.335000000000001</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>30.632999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>30.138999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
         <v>29.221</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>30.614999999999998</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>30.63</v>
       </c>
       <c r="E6">
         <v>28.925999999999998</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>30.951000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -538,41 +537,41 @@
       <c r="D7">
         <v>30.536999999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>31.042000000000002</v>
       </c>
       <c r="F7">
         <v>29.952000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>29.908000000000001</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>31.245000000000001</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>31.210999999999999</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>31.076000000000001</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>31.01</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>30.199000000000002</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>31.297999999999998</v>
       </c>
       <c r="D9">
@@ -581,21 +580,21 @@
       <c r="E9">
         <v>31.053999999999998</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>31.189</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>30.399000000000001</v>
       </c>
       <c r="C10">
         <v>31.023</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>31.399000000000001</v>
       </c>
       <c r="E10">
@@ -605,11 +604,11 @@
         <v>30.991</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>30.567</v>
       </c>
       <c r="C11">
@@ -618,18 +617,18 @@
       <c r="D11">
         <v>31.335999999999999</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>31.253</v>
       </c>
       <c r="F11">
         <v>31.048999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>30.719000000000001</v>
       </c>
       <c r="C12">
@@ -641,21 +640,21 @@
       <c r="E12">
         <v>30.646999999999998</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>31.434000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>30.838000000000001</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>31.568000000000001</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>31.5</v>
       </c>
       <c r="E13">
@@ -665,31 +664,31 @@
         <v>30.518999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>30.957000000000001</v>
       </c>
       <c r="C14">
         <v>31.492000000000001</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>31.513000000000002</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>31.268000000000001</v>
       </c>
       <c r="F14">
         <v>30.585000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>31.067</v>
       </c>
       <c r="C15">
@@ -698,18 +697,18 @@
       <c r="D15">
         <v>31.369</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>31.559000000000001</v>
       </c>
       <c r="F15">
         <v>31.363</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>31.1</v>
       </c>
       <c r="C16">
@@ -725,31 +724,31 @@
         <v>30.882999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>31.177</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>31.61</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>31.654</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>31.603999999999999</v>
       </c>
       <c r="F17">
         <v>31.248000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>31.231999999999999</v>
       </c>
       <c r="C18">
@@ -761,21 +760,21 @@
       <c r="E18">
         <v>31.5</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>31.669</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>30.983000000000001</v>
       </c>
       <c r="C19">
         <v>31.280999999999999</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>31.675999999999998</v>
       </c>
       <c r="E19">
@@ -785,7 +784,7 @@
         <v>31.591000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -805,31 +804,31 @@
         <v>31.571000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>31.324999999999999</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>31.748000000000001</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>31.712</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>31.734999999999999</v>
       </c>
       <c r="F21">
         <v>31.620999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>30.617999999999999</v>
       </c>
       <c r="C22">
@@ -841,11 +840,11 @@
       <c r="E22">
         <v>31.425000000000001</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>31.814</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -865,7 +864,7 @@
         <v>31.686</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -885,37 +884,37 @@
         <v>31.738</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>31.501999999999999</v>
       </c>
       <c r="C25">
         <v>31.716000000000001</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>31.794</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>31.808</v>
       </c>
       <c r="F25">
         <v>31.747</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>31.574000000000002</v>
       </c>
       <c r="C26">
         <v>31.72</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>31.814</v>
       </c>
       <c r="E26">
@@ -925,27 +924,27 @@
         <v>31.38</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>31.399000000000001</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>31.908000000000001</v>
       </c>
       <c r="D27">
         <v>31.751000000000001</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>31.832999999999998</v>
       </c>
       <c r="F27">
         <v>31.61</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -961,11 +960,11 @@
       <c r="E28">
         <v>31.809000000000001</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>31.940999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -975,7 +974,7 @@
       <c r="C29">
         <v>31.53</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>31.922000000000001</v>
       </c>
       <c r="E29">
@@ -985,7 +984,7 @@
         <v>31.914000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1005,7 +1004,7 @@
         <v>31.742000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1015,21 +1014,21 @@
       <c r="C31">
         <v>31.885999999999999</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>31.928999999999998</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1">
         <v>31.835999999999999</v>
       </c>
       <c r="F31">
         <v>31.29</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>31.780999999999999</v>
       </c>
       <c r="C32">
@@ -1038,18 +1037,18 @@
       <c r="D32">
         <v>31.844999999999999</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>31.922999999999998</v>
       </c>
       <c r="F32">
         <v>31.917000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>31.795000000000002</v>
       </c>
       <c r="C33">
@@ -1061,18 +1060,18 @@
       <c r="E33">
         <v>31.798999999999999</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>31.971</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>31.783000000000001</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>31.946000000000002</v>
       </c>
       <c r="D34">
@@ -1085,31 +1084,31 @@
         <v>31.74</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35">
         <v>31.814</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>32.042000000000002</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>32.003999999999998</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="1">
         <v>31.931999999999999</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>32.026000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>31.849</v>
       </c>
       <c r="C36">
@@ -1125,11 +1124,11 @@
         <v>31.826000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>31.483000000000001</v>
       </c>
       <c r="C37">
@@ -1145,7 +1144,7 @@
         <v>31.844000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1158,14 +1157,14 @@
       <c r="D38">
         <v>31.677</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>31.933</v>
       </c>
       <c r="F38">
         <v>31.864999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1181,11 +1180,11 @@
       <c r="E39">
         <v>31.817</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>32.042999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1205,11 +1204,11 @@
         <v>31.956</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>31.632999999999999</v>
       </c>
       <c r="C41">
@@ -1225,7 +1224,7 @@
         <v>31.946000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1238,18 +1237,18 @@
       <c r="D42">
         <v>31.858000000000001</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>31.977</v>
       </c>
       <c r="F42">
         <v>31.818999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>31.946000000000002</v>
       </c>
       <c r="C43">
@@ -1261,31 +1260,31 @@
       <c r="E43">
         <v>31.869</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>32.119999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>31.776</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>32.07</v>
       </c>
       <c r="D44">
         <v>31.937999999999999</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>32.046999999999997</v>
       </c>
       <c r="F44">
         <v>32.082999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1295,7 +1294,7 @@
       <c r="C45">
         <v>31.82</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>32.005000000000003</v>
       </c>
       <c r="E45">
@@ -1305,7 +1304,7 @@
         <v>29.715</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1315,7 +1314,7 @@
       <c r="C46">
         <v>31.891999999999999</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>32.024999999999999</v>
       </c>
       <c r="E46">
@@ -1325,7 +1324,7 @@
         <v>32.021999999999998</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1345,7 +1344,7 @@
         <v>32.067</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1355,7 +1354,7 @@
       <c r="C48">
         <v>31.989000000000001</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>32.072000000000003</v>
       </c>
       <c r="E48">
@@ -1365,11 +1364,11 @@
         <v>32.058999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>31.881</v>
       </c>
       <c r="C49">
@@ -1385,7 +1384,7 @@
         <v>32.027000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1405,11 +1404,11 @@
         <v>32.042999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>31.981999999999999</v>
       </c>
       <c r="C51">
@@ -1425,7 +1424,7 @@
         <v>31.971</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1435,7 +1434,7 @@
       <c r="C52">
         <v>32.024999999999999</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="1">
         <v>32.106999999999999</v>
       </c>
       <c r="E52">
@@ -1445,7 +1444,7 @@
         <v>32.018999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1458,21 +1457,21 @@
       <c r="D53">
         <v>32.058</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="1">
         <v>32.070999999999998</v>
       </c>
       <c r="F53">
         <v>32.052</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54">
         <v>31.809000000000001</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="1">
         <v>32.088000000000001</v>
       </c>
       <c r="D54">
@@ -1485,7 +1484,7 @@
         <v>32.078000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1498,18 +1497,18 @@
       <c r="D55">
         <v>31.792999999999999</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>32.085999999999999</v>
       </c>
       <c r="F55">
         <v>32.106999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>32.098999999999997</v>
       </c>
       <c r="C56">
@@ -1518,18 +1517,18 @@
       <c r="D56">
         <v>32.097999999999999</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>32.093000000000004</v>
       </c>
       <c r="F56">
         <v>31.940999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>31.969000000000001</v>
       </c>
       <c r="C57">
@@ -1545,7 +1544,7 @@
         <v>32.082000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1558,14 +1557,14 @@
       <c r="D58">
         <v>32.012</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="1">
         <v>32.124000000000002</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="1">
         <v>32.18</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1585,31 +1584,31 @@
         <v>32.088999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>32.136000000000003</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="1">
         <v>32.103000000000002</v>
       </c>
       <c r="D60">
         <v>32.018999999999998</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="1">
         <v>32.142000000000003</v>
       </c>
       <c r="F60">
         <v>31.73</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>31.99</v>
       </c>
       <c r="C61">
@@ -1625,14 +1624,14 @@
         <v>32.136000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62">
         <v>32.103000000000002</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="1">
         <v>32.15</v>
       </c>
       <c r="D62">
@@ -1645,7 +1644,7 @@
         <v>32.139000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1665,11 +1664,11 @@
         <v>31.965</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>32.134</v>
       </c>
       <c r="C64">
@@ -1685,14 +1684,14 @@
         <v>32.139000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65">
         <v>32.158999999999999</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="1">
         <v>32.158000000000001</v>
       </c>
       <c r="D65">
@@ -1705,7 +1704,7 @@
         <v>32.072000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1715,7 +1714,7 @@
       <c r="C66">
         <v>32.075000000000003</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>32.188000000000002</v>
       </c>
       <c r="E66">
@@ -1725,7 +1724,7 @@
         <v>32.136000000000003</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1741,18 +1740,18 @@
       <c r="E67">
         <v>31.943000000000001</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="1">
         <v>32.212000000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68">
         <v>32.204000000000001</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="1">
         <v>32.159999999999997</v>
       </c>
       <c r="D68">
@@ -1765,11 +1764,11 @@
         <v>32.18</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>32.177</v>
       </c>
       <c r="C69">
@@ -1781,11 +1780,11 @@
       <c r="E69">
         <v>32.122</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="1">
         <v>32.225999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1795,7 +1794,7 @@
       <c r="C70">
         <v>32.136000000000003</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>32.243000000000002</v>
       </c>
       <c r="E70">
@@ -1805,14 +1804,14 @@
         <v>32.174999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71">
         <v>32.174999999999997</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="1">
         <v>32.185000000000002</v>
       </c>
       <c r="D71">
@@ -1825,7 +1824,7 @@
         <v>32.021999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1845,7 +1844,7 @@
         <v>32.118000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>32.177</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1878,21 +1877,21 @@
       <c r="D74">
         <v>32.21</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="1">
         <v>32.180999999999997</v>
       </c>
       <c r="F74">
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>32.131</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="1">
         <v>32.215000000000003</v>
       </c>
       <c r="D75">
@@ -1905,7 +1904,7 @@
         <v>32.21</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1925,14 +1924,14 @@
         <v>32.197000000000003</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>32.264000000000003</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="1">
         <v>32.220999999999997</v>
       </c>
       <c r="D77">
@@ -1945,11 +1944,11 @@
         <v>32.218000000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>32.073999999999998</v>
       </c>
       <c r="C78">
@@ -1965,7 +1964,7 @@
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1981,11 +1980,11 @@
       <c r="E79">
         <v>32.179000000000002</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="1">
         <v>32.271999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>32.167000000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2025,7 +2024,7 @@
         <v>32.119999999999997</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2045,11 +2044,11 @@
         <v>32.235999999999997</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>32.316000000000003</v>
       </c>
       <c r="C83">
@@ -2058,24 +2057,24 @@
       <c r="D83">
         <v>32.207999999999998</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="1">
         <v>32.225000000000001</v>
       </c>
       <c r="F83">
         <v>32.045999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>32.283000000000001</v>
       </c>
       <c r="C84">
         <v>32.200000000000003</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="1">
         <v>32.255000000000003</v>
       </c>
       <c r="E84">
@@ -2085,14 +2084,14 @@
         <v>32.241</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>83</v>
       </c>
       <c r="B85">
         <v>32.295000000000002</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="1">
         <v>32.274999999999999</v>
       </c>
       <c r="D85">
@@ -2105,7 +2104,7 @@
         <v>32.219000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2145,7 +2144,7 @@
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2155,7 +2154,7 @@
       <c r="C88">
         <v>32.125999999999998</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="1">
         <v>32.307000000000002</v>
       </c>
       <c r="E88">
@@ -2165,7 +2164,7 @@
         <v>31.812999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2178,14 +2177,14 @@
       <c r="D89">
         <v>31.902000000000001</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="1">
         <v>32.270000000000003</v>
       </c>
       <c r="F89">
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2205,11 +2204,11 @@
         <v>32.095999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>32.250999999999998</v>
       </c>
       <c r="C91">
@@ -2225,7 +2224,7 @@
         <v>32.234999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>32.268999999999998</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2265,7 +2264,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2285,11 +2284,11 @@
         <v>32.164000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>32.332000000000001</v>
       </c>
       <c r="C95">
@@ -2305,7 +2304,7 @@
         <v>32.198999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>32.247</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2341,18 +2340,18 @@
       <c r="E97">
         <v>32.203000000000003</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="1">
         <v>32.320999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="B98">
         <v>32.204999999999998</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="1">
         <v>32.305999999999997</v>
       </c>
       <c r="D98">
@@ -2365,7 +2364,7 @@
         <v>32.302</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2375,17 +2374,17 @@
       <c r="C99">
         <v>32.234999999999999</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>32.338999999999999</v>
       </c>
       <c r="E99">
         <v>32.238999999999997</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="1">
         <v>32.328000000000003</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2405,14 +2404,14 @@
         <v>32.301000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="1">
         <v>32.381999999999998</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="1">
         <v>32.311999999999998</v>
       </c>
       <c r="D101">
@@ -2425,7 +2424,7 @@
         <v>32.201999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2445,7 +2444,7 @@
         <v>32.259</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2455,7 +2454,7 @@
       <c r="C103">
         <v>32.215000000000003</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="1">
         <v>32.345999999999997</v>
       </c>
       <c r="E103">
@@ -2465,14 +2464,14 @@
         <v>32.223999999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>102</v>
       </c>
       <c r="B104">
         <v>32.259</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="1">
         <v>32.332000000000001</v>
       </c>
       <c r="D104">
@@ -2485,7 +2484,7 @@
         <v>32.326999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2505,7 +2504,7 @@
         <v>32.212000000000003</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>32.048999999999999</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2538,14 +2537,14 @@
       <c r="D107">
         <v>32.046999999999997</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>32.279000000000003</v>
       </c>
       <c r="F107">
         <v>32.158999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>106</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>32.32</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>31.946000000000002</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>32.246000000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2625,7 +2624,7 @@
         <v>32.301000000000002</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2645,11 +2644,11 @@
         <v>32.030999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="1">
         <v>32.384999999999998</v>
       </c>
       <c r="C113">
@@ -2658,14 +2657,14 @@
       <c r="D113">
         <v>32.232999999999997</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="1">
         <v>32.314999999999998</v>
       </c>
       <c r="F113">
         <v>32.271000000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>32.225000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>113</v>
       </c>
@@ -2701,11 +2700,11 @@
       <c r="E115">
         <v>32.298999999999999</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="1">
         <v>32.347999999999999</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>114</v>
       </c>
@@ -2715,7 +2714,7 @@
       <c r="C116">
         <v>32.302999999999997</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="1">
         <v>32.375999999999998</v>
       </c>
       <c r="E116">
@@ -2725,7 +2724,7 @@
         <v>32.274999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>115</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>31.917000000000002</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>116</v>
       </c>
@@ -2761,11 +2760,11 @@
       <c r="E118">
         <v>32.295000000000002</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="1">
         <v>32.390999999999998</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>117</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>32.39</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>118</v>
       </c>
@@ -2805,7 +2804,7 @@
         <v>32.191000000000003</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>119</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>32.270000000000003</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>120</v>
       </c>
@@ -2845,11 +2844,11 @@
         <v>32.305999999999997</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="1">
         <v>32.466999999999999</v>
       </c>
       <c r="C123">
@@ -2865,7 +2864,7 @@
         <v>32.335000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>122</v>
       </c>
@@ -2878,18 +2877,18 @@
       <c r="D124">
         <v>32.363</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="1">
         <v>32.341999999999999</v>
       </c>
       <c r="F124">
         <v>32.229999999999997</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="1">
         <v>32.319000000000003</v>
       </c>
       <c r="C125">
@@ -2905,7 +2904,7 @@
         <v>32.329000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>124</v>
       </c>
@@ -2925,14 +2924,14 @@
         <v>32.186999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>125</v>
       </c>
       <c r="B127">
         <v>32.4</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="1">
         <v>32.347999999999999</v>
       </c>
       <c r="D127">
@@ -2945,7 +2944,7 @@
         <v>31.99</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>126</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>32.228000000000002</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>127</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>32.079000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>128</v>
       </c>
@@ -3005,7 +3004,7 @@
         <v>32.246000000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>129</v>
       </c>
@@ -3025,11 +3024,11 @@
         <v>32.226999999999997</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>130</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="1">
         <v>32.506</v>
       </c>
       <c r="C132">
@@ -3045,11 +3044,11 @@
         <v>32.350999999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>131</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="1">
         <v>32.423000000000002</v>
       </c>
       <c r="C133">
@@ -3065,7 +3064,7 @@
         <v>32.353999999999999</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>132</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>32.301000000000002</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>133</v>
       </c>
@@ -3105,11 +3104,11 @@
         <v>32.319000000000003</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="1">
         <v>32.548000000000002</v>
       </c>
       <c r="C136">
@@ -3125,11 +3124,11 @@
         <v>32.350999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>135</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="1">
         <v>32.564999999999998</v>
       </c>
       <c r="C137">
@@ -3138,18 +3137,18 @@
       <c r="D137">
         <v>32.325000000000003</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="1">
         <v>32.378</v>
       </c>
       <c r="F137">
         <v>32.238</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>136</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="1">
         <v>32.566000000000003</v>
       </c>
       <c r="C138">
@@ -3161,15 +3160,15 @@
       <c r="E138">
         <v>32.255000000000003</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="1">
         <v>32.401000000000003</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>137</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="1">
         <v>32.554000000000002</v>
       </c>
       <c r="C139">
@@ -3185,7 +3184,7 @@
         <v>32.286999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>138</v>
       </c>
@@ -3205,7 +3204,7 @@
         <v>32.323999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>139</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>32.24</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>140</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>32.344000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>141</v>
       </c>
@@ -3255,7 +3254,7 @@
       <c r="C143">
         <v>32.301000000000002</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="1">
         <v>32.427</v>
       </c>
       <c r="E143">
@@ -3265,7 +3264,7 @@
         <v>32.258000000000003</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>142</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>32.356999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>143</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>32.308999999999997</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>144</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>32.378</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>145</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>146</v>
       </c>
@@ -3365,7 +3364,7 @@
         <v>32.351999999999997</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>147</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>32.302999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>148</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>32.389000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>149</v>
       </c>
@@ -3425,14 +3424,14 @@
         <v>32.357999999999997</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>150</v>
       </c>
       <c r="B152">
         <v>32.573999999999998</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="1">
         <v>32.369</v>
       </c>
       <c r="D152">
@@ -3445,11 +3444,11 @@
         <v>32.334000000000003</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="1">
         <v>32.545000000000002</v>
       </c>
       <c r="C153">
@@ -3461,11 +3460,11 @@
       <c r="E153">
         <v>32.281999999999996</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="1">
         <v>32.412999999999997</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>152</v>
       </c>
@@ -3481,11 +3480,11 @@
       <c r="E154">
         <v>32.244</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="1">
         <v>32.414000000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>153</v>
       </c>
@@ -3501,11 +3500,11 @@
       <c r="E155">
         <v>32.372999999999998</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="1">
         <v>32.43</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>154</v>
       </c>
@@ -3525,11 +3524,11 @@
         <v>32.319000000000003</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>155</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="1">
         <v>32.575000000000003</v>
       </c>
       <c r="C157">
@@ -3545,7 +3544,7 @@
         <v>32.426000000000002</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>156</v>
       </c>
@@ -3565,11 +3564,11 @@
         <v>32.368000000000002</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>157</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="1">
         <v>32.582000000000001</v>
       </c>
       <c r="C159">
@@ -3585,7 +3584,7 @@
         <v>32.359000000000002</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>158</v>
       </c>
@@ -3605,11 +3604,11 @@
         <v>32.276000000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>159</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="1">
         <v>32.581000000000003</v>
       </c>
       <c r="C161">
@@ -3625,14 +3624,14 @@
         <v>32.402999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>160</v>
       </c>
       <c r="B162">
         <v>32.576999999999998</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C162" s="1">
         <v>32.380000000000003</v>
       </c>
       <c r="D162">
@@ -3645,7 +3644,7 @@
         <v>32.326999999999998</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>161</v>
       </c>
@@ -3665,7 +3664,7 @@
         <v>32.429000000000002</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>162</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>32.345999999999997</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>163</v>
       </c>
@@ -3705,14 +3704,14 @@
         <v>31.826000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>164</v>
       </c>
       <c r="B166">
         <v>32.555999999999997</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166" s="1">
         <v>32.393999999999998</v>
       </c>
       <c r="D166">
@@ -3725,7 +3724,7 @@
         <v>32.384999999999998</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>165</v>
       </c>
@@ -3741,11 +3740,11 @@
       <c r="E167">
         <v>32.356000000000002</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="1">
         <v>32.441000000000003</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>166</v>
       </c>
@@ -3755,7 +3754,7 @@
       <c r="C168">
         <v>32.325000000000003</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="1">
         <v>32.432000000000002</v>
       </c>
       <c r="E168">
@@ -3765,7 +3764,7 @@
         <v>32.354999999999997</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>167</v>
       </c>
@@ -3785,11 +3784,11 @@
         <v>32.378</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="1">
         <v>32.561999999999998</v>
       </c>
       <c r="C170">
@@ -3805,7 +3804,7 @@
         <v>32.363999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>169</v>
       </c>
@@ -3825,14 +3824,14 @@
         <v>32.39</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>170</v>
       </c>
       <c r="B172">
         <v>32.573</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172" s="1">
         <v>32.4</v>
       </c>
       <c r="D172">
@@ -3845,7 +3844,7 @@
         <v>32.366</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>171</v>
       </c>
@@ -3855,17 +3854,17 @@
       <c r="C173">
         <v>32.381999999999998</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="1">
         <v>32.451000000000001</v>
       </c>
       <c r="E173">
         <v>32.372999999999998</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="1">
         <v>32.451000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>172</v>
       </c>
@@ -3881,11 +3880,11 @@
       <c r="E174">
         <v>32.317999999999998</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="1">
         <v>32.470999999999997</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>173</v>
       </c>
@@ -3905,7 +3904,7 @@
         <v>32.384</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>174</v>
       </c>
@@ -3925,11 +3924,11 @@
         <v>32.174999999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>175</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C177">
@@ -3945,7 +3944,7 @@
         <v>32.350999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>176</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>32.445999999999998</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>177</v>
       </c>
@@ -3985,7 +3984,7 @@
         <v>32.409999999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>178</v>
       </c>
@@ -4005,7 +4004,7 @@
         <v>32.463999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>179</v>
       </c>
@@ -4025,7 +4024,7 @@
         <v>32.406999999999996</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>180</v>
       </c>
@@ -4045,7 +4044,7 @@
         <v>32.247</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>181</v>
       </c>
@@ -4065,7 +4064,7 @@
         <v>32.283000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>182</v>
       </c>
@@ -4081,11 +4080,11 @@
       <c r="E184">
         <v>32.225999999999999</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="1">
         <v>32.473999999999997</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>183</v>
       </c>
@@ -4105,7 +4104,7 @@
         <v>32.329000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>184</v>
       </c>
@@ -4125,11 +4124,11 @@
         <v>32.35</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>185</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="1">
         <v>32.639000000000003</v>
       </c>
       <c r="C187">
@@ -4138,18 +4137,18 @@
       <c r="D187">
         <v>32.372999999999998</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>32.395000000000003</v>
       </c>
       <c r="F187">
         <v>32.420999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>186</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="1">
         <v>32.594999999999999</v>
       </c>
       <c r="C188">
@@ -4161,11 +4160,11 @@
       <c r="E188">
         <v>32.389000000000003</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="1">
         <v>32.478000000000002</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>187</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>32.415999999999997</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>188</v>
       </c>
@@ -4198,14 +4197,14 @@
       <c r="D190">
         <v>32.417000000000002</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>32.433</v>
       </c>
       <c r="F190">
         <v>32.284999999999997</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>189</v>
       </c>
@@ -4225,14 +4224,14 @@
         <v>32.454000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>190</v>
       </c>
       <c r="B192">
         <v>32.604999999999997</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192" s="1">
         <v>32.44</v>
       </c>
       <c r="D192">
@@ -4245,7 +4244,7 @@
         <v>32.399000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>191</v>
       </c>
@@ -4265,7 +4264,7 @@
         <v>32.347000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>192</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>32.411999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>193</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>32.44</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>194</v>
       </c>
@@ -4325,11 +4324,11 @@
         <v>32.423999999999999</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>195</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C197">
@@ -4345,7 +4344,7 @@
         <v>32.436</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>196</v>
       </c>
@@ -4361,11 +4360,11 @@
       <c r="E198">
         <v>32.302999999999997</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="1">
         <v>32.479999999999997</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>197</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>32.462000000000003</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>198</v>
       </c>
@@ -4405,11 +4404,11 @@
         <v>32.392000000000003</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>199</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="1">
         <v>32.652000000000001</v>
       </c>
       <c r="C201">
@@ -4425,7 +4424,7 @@
         <v>32.445</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>200</v>
       </c>
@@ -4445,7 +4444,7 @@
         <v>32.47</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>201</v>
       </c>
@@ -4465,17 +4464,17 @@
         <v>32.350999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>202</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="1">
         <v>32.671999999999997</v>
       </c>
       <c r="C204">
         <v>32.424999999999997</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="1">
         <v>32.481000000000002</v>
       </c>
       <c r="E204">
@@ -4485,7 +4484,7 @@
         <v>32.451999999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>203</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>32.308999999999997</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>204</v>
       </c>
@@ -4525,7 +4524,7 @@
         <v>32.478999999999999</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>205</v>
       </c>
@@ -4545,7 +4544,7 @@
         <v>32.383000000000003</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>206</v>
       </c>
@@ -4565,7 +4564,7 @@
         <v>32.427999999999997</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>207</v>
       </c>
@@ -4585,11 +4584,11 @@
         <v>32.429000000000002</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>208</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="1">
         <v>32.677</v>
       </c>
       <c r="C210">
@@ -4605,7 +4604,7 @@
         <v>32.412999999999997</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>209</v>
       </c>
@@ -4625,7 +4624,7 @@
         <v>32.384</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>210</v>
       </c>
@@ -4638,18 +4637,18 @@
       <c r="D212">
         <v>32.43</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>32.442</v>
       </c>
       <c r="F212">
         <v>32.445999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>211</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213" s="1">
         <v>32.689</v>
       </c>
       <c r="C213">
@@ -4661,11 +4660,11 @@
       <c r="E213">
         <v>32.417999999999999</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="1">
         <v>32.491999999999997</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>212</v>
       </c>
@@ -4685,7 +4684,7 @@
         <v>32.412999999999997</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>213</v>
       </c>
@@ -4705,7 +4704,7 @@
         <v>32.378999999999998</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>214</v>
       </c>
@@ -4725,7 +4724,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>215</v>
       </c>
@@ -4745,7 +4744,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>216</v>
       </c>
@@ -4761,15 +4760,15 @@
       <c r="E218">
         <v>32.398000000000003</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="1">
         <v>32.494</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>217</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219" s="1">
         <v>32.661999999999999</v>
       </c>
       <c r="C219">
@@ -4785,7 +4784,7 @@
         <v>32.459000000000003</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>218</v>
       </c>
@@ -4805,14 +4804,14 @@
         <v>32.444000000000003</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>219</v>
       </c>
       <c r="B221">
         <v>32.694000000000003</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221" s="1">
         <v>32.442999999999998</v>
       </c>
       <c r="D221">
@@ -4825,7 +4824,7 @@
         <v>32.154000000000003</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>220</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>32.402999999999999</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>221</v>
       </c>
@@ -4861,11 +4860,11 @@
       <c r="E223">
         <v>32.381999999999998</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="1">
         <v>32.500999999999998</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>222</v>
       </c>
@@ -4878,18 +4877,18 @@
       <c r="D224">
         <v>32.448</v>
       </c>
-      <c r="E224" s="2">
+      <c r="E224" s="1">
         <v>32.46</v>
       </c>
       <c r="F224">
         <v>32.331000000000003</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>223</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225" s="1">
         <v>32.64</v>
       </c>
       <c r="C225">
@@ -4905,7 +4904,7 @@
         <v>32.499000000000002</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>224</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>32.442</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>225</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>32.378999999999998</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>226</v>
       </c>
@@ -4965,7 +4964,7 @@
         <v>32.412999999999997</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>227</v>
       </c>
@@ -4981,11 +4980,11 @@
       <c r="E229">
         <v>32.421999999999997</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="1">
         <v>32.524999999999999</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>228</v>
       </c>
@@ -5005,7 +5004,7 @@
         <v>32.499000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>229</v>
       </c>
@@ -5025,7 +5024,7 @@
         <v>32.430999999999997</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>230</v>
       </c>
@@ -5045,7 +5044,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>231</v>
       </c>
@@ -5065,7 +5064,7 @@
         <v>32.497999999999998</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>232</v>
       </c>
@@ -5085,14 +5084,14 @@
         <v>32.404000000000003</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>233</v>
       </c>
       <c r="B235">
         <v>32.710999999999999</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235" s="1">
         <v>32.448</v>
       </c>
       <c r="D235">
@@ -5105,14 +5104,14 @@
         <v>32.186</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>234</v>
       </c>
       <c r="B236">
         <v>32.710999999999999</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236" s="1">
         <v>32.463000000000001</v>
       </c>
       <c r="D236">
@@ -5125,7 +5124,7 @@
         <v>32.470999999999997</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>235</v>
       </c>
@@ -5145,7 +5144,7 @@
         <v>32.44</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>236</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>32.395000000000003</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>237</v>
       </c>
@@ -5185,7 +5184,7 @@
         <v>32.463000000000001</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>238</v>
       </c>
@@ -5205,7 +5204,7 @@
         <v>32.508000000000003</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>239</v>
       </c>
@@ -5225,7 +5224,7 @@
         <v>32.481000000000002</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>240</v>
       </c>
@@ -5245,7 +5244,7 @@
         <v>32.377000000000002</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>241</v>
       </c>
@@ -5255,7 +5254,7 @@
       <c r="C243">
         <v>32.447000000000003</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="1">
         <v>32.481999999999999</v>
       </c>
       <c r="E243">
@@ -5265,7 +5264,7 @@
         <v>32.404000000000003</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>242</v>
       </c>
@@ -5285,7 +5284,7 @@
         <v>32.381999999999998</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>243</v>
       </c>
@@ -5298,14 +5297,14 @@
       <c r="D245">
         <v>32.481000000000002</v>
       </c>
-      <c r="E245" s="2">
+      <c r="E245" s="1">
         <v>32.466999999999999</v>
       </c>
       <c r="F245">
         <v>32.427</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>244</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>32.423999999999999</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>245</v>
       </c>
@@ -5345,7 +5344,7 @@
         <v>32.454999999999998</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>246</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>32.439</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>247</v>
       </c>
@@ -5385,7 +5384,7 @@
         <v>32.405000000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>248</v>
       </c>
@@ -5405,7 +5404,7 @@
         <v>32.372999999999998</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>249</v>
       </c>
@@ -5425,7 +5424,7 @@
         <v>32.432000000000002</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>250</v>
       </c>
@@ -5435,7 +5434,7 @@
       <c r="C252">
         <v>32.408999999999999</v>
       </c>
-      <c r="D252" s="2">
+      <c r="D252" s="1">
         <v>32.493000000000002</v>
       </c>
       <c r="E252">
@@ -5445,7 +5444,7 @@
         <v>32.460999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>251</v>
       </c>
@@ -5465,7 +5464,7 @@
         <v>32.399000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>252</v>
       </c>
@@ -5485,7 +5484,7 @@
         <v>32.454000000000001</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>253</v>
       </c>
@@ -5498,14 +5497,14 @@
       <c r="D255">
         <v>32.420999999999999</v>
       </c>
-      <c r="E255" s="2">
+      <c r="E255" s="1">
         <v>32.469000000000001</v>
       </c>
       <c r="F255">
         <v>32.436</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>254</v>
       </c>
@@ -5518,14 +5517,14 @@
       <c r="D256">
         <v>32.459000000000003</v>
       </c>
-      <c r="E256" s="2">
+      <c r="E256" s="1">
         <v>32.470999999999997</v>
       </c>
       <c r="F256">
         <v>32.408999999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>255</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>32.472000000000001</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>256</v>
       </c>
@@ -5565,7 +5564,7 @@
         <v>32.502000000000002</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>257</v>
       </c>
@@ -5585,7 +5584,7 @@
         <v>32.448999999999998</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>258</v>
       </c>
@@ -5605,7 +5604,7 @@
         <v>32.436</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>259</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>260</v>
       </c>
@@ -5645,7 +5644,7 @@
         <v>32.438000000000002</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>261</v>
       </c>
@@ -5665,14 +5664,14 @@
         <v>32.478999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>262</v>
       </c>
       <c r="B264">
         <v>32.612000000000002</v>
       </c>
-      <c r="C264" s="3">
+      <c r="C264" s="1">
         <v>32.505000000000003</v>
       </c>
       <c r="D264">
@@ -5685,7 +5684,7 @@
         <v>32.511000000000003</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>263</v>
       </c>
@@ -5705,7 +5704,7 @@
         <v>32.399000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>264</v>
       </c>
@@ -5725,7 +5724,7 @@
         <v>32.469000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>265</v>
       </c>
@@ -5745,7 +5744,7 @@
         <v>32.500999999999998</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>266</v>
       </c>
@@ -5765,7 +5764,7 @@
         <v>32.479999999999997</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>267</v>
       </c>
@@ -5785,7 +5784,7 @@
         <v>32.475000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>268</v>
       </c>
@@ -5805,7 +5804,7 @@
         <v>32.515999999999998</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>269</v>
       </c>
@@ -5825,7 +5824,7 @@
         <v>32.424999999999997</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>270</v>
       </c>
@@ -5845,7 +5844,7 @@
         <v>32.347999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>271</v>
       </c>
@@ -5865,7 +5864,7 @@
         <v>32.475000000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>272</v>
       </c>
@@ -5885,7 +5884,7 @@
         <v>32.493000000000002</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>273</v>
       </c>
@@ -5905,7 +5904,7 @@
         <v>32.479999999999997</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>274</v>
       </c>
@@ -5921,11 +5920,11 @@
       <c r="E276">
         <v>32.445999999999998</v>
       </c>
-      <c r="F276" s="2">
+      <c r="F276" s="1">
         <v>32.533999999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>275</v>
       </c>
@@ -5945,7 +5944,7 @@
         <v>32.496000000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>276</v>
       </c>
@@ -5958,14 +5957,14 @@
       <c r="D278">
         <v>32.46</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>32.476999999999997</v>
       </c>
       <c r="F278">
         <v>32.494</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>277</v>
       </c>
@@ -5985,7 +5984,7 @@
         <v>32.509</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>278</v>
       </c>
@@ -6005,7 +6004,7 @@
         <v>32.389000000000003</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>279</v>
       </c>
@@ -6018,14 +6017,14 @@
       <c r="D281">
         <v>32.441000000000003</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>32.481999999999999</v>
       </c>
-      <c r="F281" s="3">
+      <c r="F281" s="1">
         <v>32.545000000000002</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>280</v>
       </c>
@@ -6035,7 +6034,7 @@
       <c r="C282">
         <v>32.296999999999997</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="1">
         <v>32.5</v>
       </c>
       <c r="E282">
@@ -6045,7 +6044,7 @@
         <v>32.543999999999997</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>281</v>
       </c>
@@ -6055,7 +6054,7 @@
       <c r="C283">
         <v>32.465000000000003</v>
       </c>
-      <c r="D283" s="3">
+      <c r="D283" s="1">
         <v>32.526000000000003</v>
       </c>
       <c r="E283">
@@ -6065,7 +6064,7 @@
         <v>32.444000000000003</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>282</v>
       </c>
@@ -6085,7 +6084,7 @@
         <v>32.523000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>283</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>32.457000000000001</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>284</v>
       </c>
@@ -6125,7 +6124,7 @@
         <v>32.463999999999999</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>285</v>
       </c>
@@ -6138,14 +6137,14 @@
       <c r="D287">
         <v>32.445999999999998</v>
       </c>
-      <c r="E287" s="2">
+      <c r="E287" s="1">
         <v>32.493000000000002</v>
       </c>
       <c r="F287">
         <v>32.53</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>286</v>
       </c>
@@ -6165,11 +6164,11 @@
         <v>32.481000000000002</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>287</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="1">
         <v>32.706000000000003</v>
       </c>
       <c r="C289">
@@ -6185,7 +6184,7 @@
         <v>32.497999999999998</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>288</v>
       </c>
@@ -6205,11 +6204,11 @@
         <v>32.473999999999997</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>289</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="1">
         <v>32.725000000000001</v>
       </c>
       <c r="C291">
@@ -6225,7 +6224,7 @@
         <v>32.524000000000001</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>290</v>
       </c>
@@ -6245,11 +6244,11 @@
         <v>32.524999999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>291</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="1">
         <v>32.71</v>
       </c>
       <c r="C293">
@@ -6265,7 +6264,7 @@
         <v>32.423000000000002</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -6285,7 +6284,7 @@
         <v>32.524000000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -6305,11 +6304,11 @@
         <v>32.444000000000003</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296" s="1">
         <v>32.744999999999997</v>
       </c>
       <c r="C296">
@@ -6325,11 +6324,11 @@
         <v>32.453000000000003</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297" s="1">
         <v>32.755000000000003</v>
       </c>
       <c r="C297">
@@ -6345,11 +6344,11 @@
         <v>32.497</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298" s="1">
         <v>32.767000000000003</v>
       </c>
       <c r="C298">
@@ -6365,7 +6364,7 @@
         <v>32.491999999999997</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -6385,7 +6384,7 @@
         <v>32.396000000000001</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -6405,7 +6404,7 @@
         <v>32.534999999999997</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -6425,43 +6424,2205 @@
         <v>32.451999999999998</v>
       </c>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B312" s="2"/>
-    </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B313" s="2"/>
-    </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B327" s="2"/>
-    </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E328" s="2"/>
-    </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B344" s="2"/>
-      <c r="E344" s="2"/>
-    </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B353" s="2"/>
-    </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E365" s="2"/>
-    </row>
-    <row r="379" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B379" s="2"/>
-    </row>
-    <row r="390" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B390" s="2"/>
-    </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
-      <c r="E407" s="3"/>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C302">
+        <v>32.402999999999999</v>
+      </c>
+      <c r="D302">
+        <v>32.445</v>
+      </c>
+      <c r="E302">
+        <v>32.456000000000003</v>
+      </c>
+      <c r="F302">
+        <v>32.070999999999998</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C303">
+        <v>31.962</v>
+      </c>
+      <c r="D303">
+        <v>32.369999999999997</v>
+      </c>
+      <c r="E303">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="F303">
+        <v>32.466999999999999</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C304">
+        <v>32.435000000000002</v>
+      </c>
+      <c r="D304">
+        <v>32.484999999999999</v>
+      </c>
+      <c r="E304">
+        <v>32.414000000000001</v>
+      </c>
+      <c r="F304">
+        <v>32.475000000000001</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>32.749000000000002</v>
+      </c>
+      <c r="C305">
+        <v>32.463999999999999</v>
+      </c>
+      <c r="D305" s="1">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="E305">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="F305">
+        <v>32.512</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>32.753999999999998</v>
+      </c>
+      <c r="C306">
+        <v>32.371000000000002</v>
+      </c>
+      <c r="D306">
+        <v>32.301000000000002</v>
+      </c>
+      <c r="E306">
+        <v>32.372999999999998</v>
+      </c>
+      <c r="F306">
+        <v>32.491</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>32.756</v>
+      </c>
+      <c r="C307">
+        <v>32.478000000000002</v>
+      </c>
+      <c r="D307">
+        <v>32.463999999999999</v>
+      </c>
+      <c r="E307">
+        <v>32.402999999999999</v>
+      </c>
+      <c r="F307">
+        <v>32.515000000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>32.756</v>
+      </c>
+      <c r="C308">
+        <v>32.445</v>
+      </c>
+      <c r="D308">
+        <v>32.465000000000003</v>
+      </c>
+      <c r="E308">
+        <v>32.466999999999999</v>
+      </c>
+      <c r="F308">
+        <v>32.542999999999999</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>32.759</v>
+      </c>
+      <c r="C309" s="1">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="D309">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="E309">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="F309">
+        <v>32.527000000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>32.76</v>
+      </c>
+      <c r="C310">
+        <v>32.445</v>
+      </c>
+      <c r="D310">
+        <v>32.470999999999997</v>
+      </c>
+      <c r="E310">
+        <v>32.406999999999996</v>
+      </c>
+      <c r="F310">
+        <v>32.508000000000003</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C311">
+        <v>32.273000000000003</v>
+      </c>
+      <c r="D311">
+        <v>32.408000000000001</v>
+      </c>
+      <c r="E311">
+        <v>32.392000000000003</v>
+      </c>
+      <c r="F311">
+        <v>32.472000000000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C312">
+        <v>32.51</v>
+      </c>
+      <c r="D312">
+        <v>32.503</v>
+      </c>
+      <c r="E312">
+        <v>32.340000000000003</v>
+      </c>
+      <c r="F312">
+        <v>32.515999999999998</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C313">
+        <v>32.423999999999999</v>
+      </c>
+      <c r="D313">
+        <v>32.473999999999997</v>
+      </c>
+      <c r="E313">
+        <v>32.436</v>
+      </c>
+      <c r="F313">
+        <v>32.344999999999999</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C314">
+        <v>32.4</v>
+      </c>
+      <c r="D314">
+        <v>32.463999999999999</v>
+      </c>
+      <c r="E314">
+        <v>32.402000000000001</v>
+      </c>
+      <c r="F314">
+        <v>32.527000000000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C315">
+        <v>32.432000000000002</v>
+      </c>
+      <c r="D315">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="E315">
+        <v>32.436999999999998</v>
+      </c>
+      <c r="F315">
+        <v>32.457999999999998</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" s="1">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C316">
+        <v>32.29</v>
+      </c>
+      <c r="D316">
+        <v>32.460999999999999</v>
+      </c>
+      <c r="E316">
+        <v>32.417999999999999</v>
+      </c>
+      <c r="F316">
+        <v>32.521999999999998</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C317">
+        <v>32.478000000000002</v>
+      </c>
+      <c r="D317">
+        <v>32.524000000000001</v>
+      </c>
+      <c r="E317">
+        <v>32.454999999999998</v>
+      </c>
+      <c r="F317">
+        <v>32.323999999999998</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>32.761000000000003</v>
+      </c>
+      <c r="C318">
+        <v>32.429000000000002</v>
+      </c>
+      <c r="D318">
+        <v>32.491</v>
+      </c>
+      <c r="E318">
+        <v>32.317</v>
+      </c>
+      <c r="F318">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>32.753</v>
+      </c>
+      <c r="C319">
+        <v>32.228999999999999</v>
+      </c>
+      <c r="D319">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="E319">
+        <v>32.392000000000003</v>
+      </c>
+      <c r="F319">
+        <v>32.487000000000002</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C320">
+        <v>32.448999999999998</v>
+      </c>
+      <c r="D320">
+        <v>32.5</v>
+      </c>
+      <c r="E320">
+        <v>32.432000000000002</v>
+      </c>
+      <c r="F320">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" s="1">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C321">
+        <v>32.377000000000002</v>
+      </c>
+      <c r="D321">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="E321">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="F321">
+        <v>32.325000000000003</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C322">
+        <v>32.426000000000002</v>
+      </c>
+      <c r="D322">
+        <v>32.433999999999997</v>
+      </c>
+      <c r="E322">
+        <v>32.4</v>
+      </c>
+      <c r="F322" s="1">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C323">
+        <v>32.337000000000003</v>
+      </c>
+      <c r="D323">
+        <v>32.442</v>
+      </c>
+      <c r="E323">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="F323">
+        <v>32.517000000000003</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C324">
+        <v>32.460999999999999</v>
+      </c>
+      <c r="D324">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="E324">
+        <v>32.453000000000003</v>
+      </c>
+      <c r="F324">
+        <v>32.478000000000002</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>32.750999999999998</v>
+      </c>
+      <c r="C325">
+        <v>32.039000000000001</v>
+      </c>
+      <c r="D325">
+        <v>32.427</v>
+      </c>
+      <c r="E325">
+        <v>32.417999999999999</v>
+      </c>
+      <c r="F325">
+        <v>32.503999999999998</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>32.72</v>
+      </c>
+      <c r="C326">
+        <v>32.463999999999999</v>
+      </c>
+      <c r="D326">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="E326">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="F326">
+        <v>32.512999999999998</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" s="1">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C327">
+        <v>32.46</v>
+      </c>
+      <c r="D327">
+        <v>32.481000000000002</v>
+      </c>
+      <c r="E327">
+        <v>32.487000000000002</v>
+      </c>
+      <c r="F327">
+        <v>32.487000000000002</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C328">
+        <v>32.097999999999999</v>
+      </c>
+      <c r="D328">
+        <v>32.463000000000001</v>
+      </c>
+      <c r="E328" s="1">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="F328">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>32.76</v>
+      </c>
+      <c r="C329">
+        <v>32.189</v>
+      </c>
+      <c r="D329" s="1">
+        <v>32.54</v>
+      </c>
+      <c r="E329">
+        <v>32.411999999999999</v>
+      </c>
+      <c r="F329">
+        <v>32.552</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C330">
+        <v>32.46</v>
+      </c>
+      <c r="D330">
+        <v>32.451000000000001</v>
+      </c>
+      <c r="E330">
+        <v>32.418999999999997</v>
+      </c>
+      <c r="F330">
+        <v>32.51</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C331">
+        <v>32.426000000000002</v>
+      </c>
+      <c r="D331">
+        <v>32.46</v>
+      </c>
+      <c r="E331">
+        <v>32.338999999999999</v>
+      </c>
+      <c r="F331">
+        <v>32.171999999999997</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C332">
+        <v>32.465000000000003</v>
+      </c>
+      <c r="D332">
+        <v>32.524000000000001</v>
+      </c>
+      <c r="E332">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="F332">
+        <v>32.466999999999999</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C333">
+        <v>32.439</v>
+      </c>
+      <c r="D333">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="E333">
+        <v>32.451999999999998</v>
+      </c>
+      <c r="F333" s="1">
+        <v>32.567</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C334">
+        <v>32.457999999999998</v>
+      </c>
+      <c r="D334">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="E334">
+        <v>32.420999999999999</v>
+      </c>
+      <c r="F334">
+        <v>32.411000000000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>32.76</v>
+      </c>
+      <c r="C335">
+        <v>32.475000000000001</v>
+      </c>
+      <c r="D335">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E335">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="F335">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C336">
+        <v>32.472000000000001</v>
+      </c>
+      <c r="D336" s="1">
+        <v>32.548000000000002</v>
+      </c>
+      <c r="E336">
+        <v>32.412999999999997</v>
+      </c>
+      <c r="F336">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C337">
+        <v>32.454999999999998</v>
+      </c>
+      <c r="D337">
+        <v>32.512999999999998</v>
+      </c>
+      <c r="E337">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="F337">
+        <v>32.436999999999998</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C338">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="D338">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="E338">
+        <v>32.466999999999999</v>
+      </c>
+      <c r="F338">
+        <v>32.511000000000003</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C339">
+        <v>32.503</v>
+      </c>
+      <c r="D339">
+        <v>32.46</v>
+      </c>
+      <c r="E339">
+        <v>32.454000000000001</v>
+      </c>
+      <c r="F339" s="2">
+        <v>32.57</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>32.738999999999997</v>
+      </c>
+      <c r="C340">
+        <v>32.368000000000002</v>
+      </c>
+      <c r="D340">
+        <v>32.442</v>
+      </c>
+      <c r="E340">
+        <v>32.405000000000001</v>
+      </c>
+      <c r="F340">
+        <v>32.543999999999997</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>32.773000000000003</v>
+      </c>
+      <c r="C341">
+        <v>32.456000000000003</v>
+      </c>
+      <c r="D341">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E341">
+        <v>32.335000000000001</v>
+      </c>
+      <c r="F341">
+        <v>32.49</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>32.731999999999999</v>
+      </c>
+      <c r="C342">
+        <v>32.465000000000003</v>
+      </c>
+      <c r="D342">
+        <v>32.44</v>
+      </c>
+      <c r="E342">
+        <v>32.444000000000003</v>
+      </c>
+      <c r="F342">
+        <v>32.512999999999998</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C343">
+        <v>32.438000000000002</v>
+      </c>
+      <c r="D343">
+        <v>32.497</v>
+      </c>
+      <c r="E343">
+        <v>32.448</v>
+      </c>
+      <c r="F343">
+        <v>32.561</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="1">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C344">
+        <v>32.42</v>
+      </c>
+      <c r="D344">
+        <v>32.399000000000001</v>
+      </c>
+      <c r="E344" s="1">
+        <v>32.518999999999998</v>
+      </c>
+      <c r="F344">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C345">
+        <v>32.366</v>
+      </c>
+      <c r="D345">
+        <v>32.414000000000001</v>
+      </c>
+      <c r="E345">
+        <v>32.5</v>
+      </c>
+      <c r="F345">
+        <v>32.253</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C346">
+        <v>32.463000000000001</v>
+      </c>
+      <c r="D346">
+        <v>32.521999999999998</v>
+      </c>
+      <c r="E346">
+        <v>32.448</v>
+      </c>
+      <c r="F346">
+        <v>32.512</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C347" s="1">
+        <v>32.523000000000003</v>
+      </c>
+      <c r="D347">
+        <v>32.439</v>
+      </c>
+      <c r="E347">
+        <v>32.395000000000003</v>
+      </c>
+      <c r="F347">
+        <v>32.499000000000002</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>32.764000000000003</v>
+      </c>
+      <c r="C348">
+        <v>32.47</v>
+      </c>
+      <c r="D348">
+        <v>32.521000000000001</v>
+      </c>
+      <c r="E348">
+        <v>32.441000000000003</v>
+      </c>
+      <c r="F348">
+        <v>32.475000000000001</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>32.756999999999998</v>
+      </c>
+      <c r="C349">
+        <v>32.441000000000003</v>
+      </c>
+      <c r="D349">
+        <v>32.521000000000001</v>
+      </c>
+      <c r="E349">
+        <v>32.417999999999999</v>
+      </c>
+      <c r="F349">
+        <v>32.521000000000001</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>32.762</v>
+      </c>
+      <c r="C350">
+        <v>32.456000000000003</v>
+      </c>
+      <c r="D350">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E350">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="F350">
+        <v>32.558</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C351">
+        <v>32.460999999999999</v>
+      </c>
+      <c r="D351">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="E351">
+        <v>32.466999999999999</v>
+      </c>
+      <c r="F351">
+        <v>32.536000000000001</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>32.78</v>
+      </c>
+      <c r="C352">
+        <v>32.454999999999998</v>
+      </c>
+      <c r="D352">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="E352">
+        <v>32.506</v>
+      </c>
+      <c r="F352">
+        <v>32.363999999999997</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="1">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C353">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="D353">
+        <v>32.540999999999997</v>
+      </c>
+      <c r="E353">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="F353">
+        <v>32.459000000000003</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C354" s="1">
+        <v>32.524000000000001</v>
+      </c>
+      <c r="D354">
+        <v>32.433999999999997</v>
+      </c>
+      <c r="E354">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="F354">
+        <v>32.456000000000003</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C355">
+        <v>32.427</v>
+      </c>
+      <c r="D355">
+        <v>32.488999999999997</v>
+      </c>
+      <c r="E355">
+        <v>32.424999999999997</v>
+      </c>
+      <c r="F355">
+        <v>32.517000000000003</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C356">
+        <v>32.395000000000003</v>
+      </c>
+      <c r="D356">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="E356">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="F356">
+        <v>32.497</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C357">
+        <v>32.366</v>
+      </c>
+      <c r="D357">
+        <v>32.363999999999997</v>
+      </c>
+      <c r="E357">
+        <v>32.497</v>
+      </c>
+      <c r="F357">
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C358">
+        <v>32.429000000000002</v>
+      </c>
+      <c r="D358">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="E358">
+        <v>32.478999999999999</v>
+      </c>
+      <c r="F358">
+        <v>32.493000000000002</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C359">
+        <v>32.415999999999997</v>
+      </c>
+      <c r="D359">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="E359">
+        <v>32.473999999999997</v>
+      </c>
+      <c r="F359">
+        <v>32.527999999999999</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C360">
+        <v>32.453000000000003</v>
+      </c>
+      <c r="D360">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="E360">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="F360">
+        <v>32.491</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>32.79</v>
+      </c>
+      <c r="C361">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D361">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="E361">
+        <v>32.433</v>
+      </c>
+      <c r="F361">
+        <v>32.481999999999999</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C362">
+        <v>32.448</v>
+      </c>
+      <c r="D362">
+        <v>32.396000000000001</v>
+      </c>
+      <c r="E362">
+        <v>32.49</v>
+      </c>
+      <c r="F362">
+        <v>32.475000000000001</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C363">
+        <v>32.462000000000003</v>
+      </c>
+      <c r="D363">
+        <v>32.444000000000003</v>
+      </c>
+      <c r="E363">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="F363">
+        <v>32.456000000000003</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C364">
+        <v>32.435000000000002</v>
+      </c>
+      <c r="D364">
+        <v>32.512</v>
+      </c>
+      <c r="E364">
+        <v>32.387999999999998</v>
+      </c>
+      <c r="F364">
+        <v>32.515999999999998</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C365">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="D365">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E365" s="1">
+        <v>32.520000000000003</v>
+      </c>
+      <c r="F365">
+        <v>32.512999999999998</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C366">
+        <v>32.497</v>
+      </c>
+      <c r="D366">
+        <v>32.506</v>
+      </c>
+      <c r="E366">
+        <v>32.451000000000001</v>
+      </c>
+      <c r="F366">
+        <v>32.533999999999999</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C367">
+        <v>32.487000000000002</v>
+      </c>
+      <c r="D367">
+        <v>32.503</v>
+      </c>
+      <c r="E367">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="F367">
+        <v>32.545999999999999</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>32.774999999999999</v>
+      </c>
+      <c r="C368">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="D368">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E368">
+        <v>32.409999999999997</v>
+      </c>
+      <c r="F368">
+        <v>32.563000000000002</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C369">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="D369">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="E369">
+        <v>32.445999999999998</v>
+      </c>
+      <c r="F369">
+        <v>32.523000000000003</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C370">
+        <v>32.432000000000002</v>
+      </c>
+      <c r="D370">
+        <v>32.542000000000002</v>
+      </c>
+      <c r="E370">
+        <v>32.409999999999997</v>
+      </c>
+      <c r="F370">
+        <v>32.503999999999998</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C371">
+        <v>32.475000000000001</v>
+      </c>
+      <c r="D371">
+        <v>32.448999999999998</v>
+      </c>
+      <c r="E371">
+        <v>32.448999999999998</v>
+      </c>
+      <c r="F371">
+        <v>32.524999999999999</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>32.78</v>
+      </c>
+      <c r="C372">
+        <v>32.481999999999999</v>
+      </c>
+      <c r="D372">
+        <v>32.433999999999997</v>
+      </c>
+      <c r="E372">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="F372">
+        <v>32.488</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C373">
+        <v>32.417000000000002</v>
+      </c>
+      <c r="D373">
+        <v>32.503</v>
+      </c>
+      <c r="E373">
+        <v>32.454000000000001</v>
+      </c>
+      <c r="F373">
+        <v>32.546999999999997</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>32.786000000000001</v>
+      </c>
+      <c r="C374">
+        <v>32.390999999999998</v>
+      </c>
+      <c r="D374">
+        <v>32.502000000000002</v>
+      </c>
+      <c r="E374">
+        <v>32.491</v>
+      </c>
+      <c r="F374">
+        <v>32.542000000000002</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C375">
+        <v>32.514000000000003</v>
+      </c>
+      <c r="D375">
+        <v>32.438000000000002</v>
+      </c>
+      <c r="E375">
+        <v>32.404000000000003</v>
+      </c>
+      <c r="F375">
+        <v>32.473999999999997</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C376">
+        <v>32.49</v>
+      </c>
+      <c r="D376">
+        <v>32.506</v>
+      </c>
+      <c r="E376">
+        <v>32.494</v>
+      </c>
+      <c r="F376">
+        <v>32.465000000000003</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C377">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="D377">
+        <v>32.523000000000003</v>
+      </c>
+      <c r="E377">
+        <v>32.457999999999998</v>
+      </c>
+      <c r="F377">
+        <v>32.542000000000002</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>32.78</v>
+      </c>
+      <c r="C378">
+        <v>32.512999999999998</v>
+      </c>
+      <c r="D378">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="E378">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="F378">
+        <v>32.530999999999999</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="1">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C379">
+        <v>32.463000000000001</v>
+      </c>
+      <c r="D379">
+        <v>32.465000000000003</v>
+      </c>
+      <c r="E379">
+        <v>32.415999999999997</v>
+      </c>
+      <c r="F379">
+        <v>32.542000000000002</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C380">
+        <v>32.518000000000001</v>
+      </c>
+      <c r="D380" s="1">
+        <v>32.56</v>
+      </c>
+      <c r="E380">
+        <v>32.451000000000001</v>
+      </c>
+      <c r="F380">
+        <v>32.557000000000002</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C381">
+        <v>32.420999999999999</v>
+      </c>
+      <c r="D381">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E381">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="F381">
+        <v>32.453000000000003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C382">
+        <v>32.42</v>
+      </c>
+      <c r="D382">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E382">
+        <v>32.5</v>
+      </c>
+      <c r="F382">
+        <v>32.390999999999998</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C383" s="1">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="D383">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E383">
+        <v>32.517000000000003</v>
+      </c>
+      <c r="F383">
+        <v>32.481000000000002</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C384">
+        <v>32.487000000000002</v>
+      </c>
+      <c r="D384">
+        <v>32.518000000000001</v>
+      </c>
+      <c r="E384">
+        <v>32.5</v>
+      </c>
+      <c r="F384">
+        <v>32.527999999999999</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C385" s="1">
+        <v>32.536000000000001</v>
+      </c>
+      <c r="D385">
+        <v>32.484999999999999</v>
+      </c>
+      <c r="E385">
+        <v>32.460999999999999</v>
+      </c>
+      <c r="F385">
+        <v>32.508000000000003</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C386">
+        <v>32.365000000000002</v>
+      </c>
+      <c r="D386">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="E386">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="F386">
+        <v>32.546999999999997</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C387">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D387">
+        <v>32.472000000000001</v>
+      </c>
+      <c r="E387">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="F387">
+        <v>32.548999999999999</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C388">
+        <v>32.424999999999997</v>
+      </c>
+      <c r="D388">
+        <v>32.484999999999999</v>
+      </c>
+      <c r="E388">
+        <v>32.481999999999999</v>
+      </c>
+      <c r="F388">
+        <v>32.527999999999999</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C389">
+        <v>32.439</v>
+      </c>
+      <c r="D389">
+        <v>32.534999999999997</v>
+      </c>
+      <c r="E389">
+        <v>32.475000000000001</v>
+      </c>
+      <c r="F389">
+        <v>32.567</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="1">
+        <v>32.802999999999997</v>
+      </c>
+      <c r="C390">
+        <v>32.462000000000003</v>
+      </c>
+      <c r="D390">
+        <v>32.454000000000001</v>
+      </c>
+      <c r="E390">
+        <v>32.47</v>
+      </c>
+      <c r="F390">
+        <v>32.499000000000002</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C391">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="D391">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="E391">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="F391">
+        <v>32.546999999999997</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C392">
+        <v>32.414000000000001</v>
+      </c>
+      <c r="D392">
+        <v>32.426000000000002</v>
+      </c>
+      <c r="E392">
+        <v>32.475000000000001</v>
+      </c>
+      <c r="F392">
+        <v>32.552999999999997</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C393">
+        <v>32.497</v>
+      </c>
+      <c r="D393">
+        <v>32.447000000000003</v>
+      </c>
+      <c r="E393">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="F393">
+        <v>32.517000000000003</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C394">
+        <v>32.445999999999998</v>
+      </c>
+      <c r="D394">
+        <v>32.430999999999997</v>
+      </c>
+      <c r="E394">
+        <v>32.436</v>
+      </c>
+      <c r="F394">
+        <v>32.512999999999998</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C395">
+        <v>32.421999999999997</v>
+      </c>
+      <c r="D395">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="E395">
+        <v>32.470999999999997</v>
+      </c>
+      <c r="F395">
+        <v>32.500999999999998</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>32.78</v>
+      </c>
+      <c r="C396">
+        <v>32.470999999999997</v>
+      </c>
+      <c r="D396">
+        <v>32.454000000000001</v>
+      </c>
+      <c r="E396">
+        <v>32.46</v>
+      </c>
+      <c r="F396">
+        <v>32.466999999999999</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C397">
+        <v>32.371000000000002</v>
+      </c>
+      <c r="D397">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="E397">
+        <v>32.406999999999996</v>
+      </c>
+      <c r="F397">
+        <v>32.534999999999997</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C398">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="D398">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="E398">
+        <v>32.412999999999997</v>
+      </c>
+      <c r="F398">
+        <v>32.533000000000001</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>32.78</v>
+      </c>
+      <c r="C399">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D399">
+        <v>32.459000000000003</v>
+      </c>
+      <c r="E399">
+        <v>32.488</v>
+      </c>
+      <c r="F399">
+        <v>32.539000000000001</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C400">
+        <v>32.481000000000002</v>
+      </c>
+      <c r="D400">
+        <v>32.463999999999999</v>
+      </c>
+      <c r="E400">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="F400">
+        <v>32.524000000000001</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C401">
+        <v>32.51</v>
+      </c>
+      <c r="D401">
+        <v>32.472000000000001</v>
+      </c>
+      <c r="E401">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="F401">
+        <v>32.549999999999997</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C402">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="D402" s="1">
+        <v>32.564</v>
+      </c>
+      <c r="E402">
+        <v>32.481999999999999</v>
+      </c>
+      <c r="F402">
+        <v>32.533000000000001</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C403">
+        <v>32.418999999999997</v>
+      </c>
+      <c r="D403">
+        <v>32.51</v>
+      </c>
+      <c r="E403">
+        <v>32.47</v>
+      </c>
+      <c r="F403">
+        <v>32.524999999999999</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C404">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="D404">
+        <v>32.540999999999997</v>
+      </c>
+      <c r="E404">
+        <v>32.453000000000003</v>
+      </c>
+      <c r="F404">
+        <v>32.558999999999997</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C405" s="2">
+        <v>32.537999999999997</v>
+      </c>
+      <c r="D405">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="E405">
+        <v>32.481999999999999</v>
+      </c>
+      <c r="F405">
+        <v>32.473999999999997</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C406">
+        <v>32.488999999999997</v>
+      </c>
+      <c r="D406">
+        <v>32.469000000000001</v>
+      </c>
+      <c r="E406">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="F406">
+        <v>32.465000000000003</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="2">
+        <v>32.804000000000002</v>
+      </c>
+      <c r="C407">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="D407">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="E407" s="2">
+        <v>32.554000000000002</v>
+      </c>
+      <c r="F407">
+        <v>32.511000000000003</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C408">
+        <v>32.509</v>
+      </c>
+      <c r="D408" s="2">
+        <v>32.573</v>
+      </c>
+      <c r="E408">
+        <v>32.456000000000003</v>
+      </c>
+      <c r="F408">
+        <v>32.51</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C409">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D409">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="E409">
+        <v>32.47</v>
+      </c>
+      <c r="F409">
+        <v>32.32</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C410">
+        <v>32.32</v>
+      </c>
+      <c r="D410">
+        <v>32.502000000000002</v>
+      </c>
+      <c r="E410">
+        <v>32.512999999999998</v>
+      </c>
+      <c r="F410">
+        <v>32.564</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C411">
+        <v>32.515000000000001</v>
+      </c>
+      <c r="D411">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="E411">
+        <v>32.485999999999997</v>
+      </c>
+      <c r="F411">
+        <v>32.533999999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
